--- a/术语表.xlsx
+++ b/术语表.xlsx
@@ -620,36 +620,36 @@
       <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ヒアデス</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>毕宿星团</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Hyades</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1620,36 +1620,36 @@
       <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>テラ</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>巨(Tera)</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>巨</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
+      <c r="F36" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2612,36 +2612,36 @@
       <c r="H66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>パワハラ</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>职权骚扰</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>职场霸凌</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="F67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2772,36 +2772,36 @@
       <c r="H71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>カウキャッチャー</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>火车排障器</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>排障器</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr"/>
+      <c r="F72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3220,36 +3220,36 @@
       <c r="H85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>ガウスメーター</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>高斯计</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Gaussmeter</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr"/>
+      <c r="F86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>铃木</t>
+          <t>Suzuki（车辆/品牌）</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -3668,36 +3668,36 @@
       <c r="H99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>タネガ・ブルウ・ジュウベエ</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>种子岛・Blue・十兵卫</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>种子岛・蓝・十兵卫</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>假名词</t>
         </is>
       </c>
-      <c r="E100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr"/>
+      <c r="E100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -4670,36 +4670,36 @@
       <c r="H130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>イラ壁</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>捶墙(イラ壁)</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>捶墙</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="E131" s="4" t="n">
+      <c r="E131" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+      <c r="F131" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -4894,36 +4894,36 @@
       <c r="H137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="n">
+      <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>顎クイ</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>颚咚</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>抬下巴</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="E138" s="4" t="n">
+      <c r="E138" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr"/>
+      <c r="F138" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -5214,36 +5214,36 @@
       <c r="H147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="n">
+      <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>レーザー光送電</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>激光送电</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>激光供电</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr"/>
+      <c r="F148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -5982,36 +5982,36 @@
       <c r="H171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="n">
+      <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>ソース(情報)</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>来源(信息)</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="E172" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr"/>
+      <c r="E172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -7710,36 +7710,36 @@
       <c r="H225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="4" t="n">
+      <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="B226" s="4" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>バトロボ会場</t>
         </is>
       </c>
-      <c r="C226" s="4" t="inlineStr">
-        <is>
-          <t>机器人对战会场</t>
-        </is>
-      </c>
-      <c r="D226" s="4" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>机斗会场</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E226" s="4" t="n">
+      <c r="E226" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F226" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="inlineStr"/>
+      <c r="F226" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -7998,36 +7998,36 @@
       <c r="H234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="n">
+      <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
-      <c r="B235" s="4" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>日ポみなと公園</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr">
-        <is>
-          <t>日葡合作港口公园</t>
-        </is>
-      </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>日葡港公园</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E235" s="4" t="n">
+      <c r="E235" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F235" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr"/>
+      <c r="F235" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -8350,36 +8350,36 @@
       <c r="H245" s="3" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="4" t="n">
+      <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>アリエル</t>
         </is>
       </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>艾莉尔</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Ariel</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E246" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F246" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="inlineStr"/>
+      <c r="E246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -8894,36 +8894,36 @@
       <c r="H262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="4" t="n">
+      <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
-      <c r="B263" s="4" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>中央駅</t>
         </is>
       </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>中央车站</t>
-        </is>
-      </c>
-      <c r="D263" s="4" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>中央站</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E263" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F263" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H263" s="5" t="inlineStr"/>
+      <c r="E263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -9342,36 +9342,36 @@
       <c r="H276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="4" t="n">
+      <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
-      <c r="B277" s="4" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>島間崎</t>
         </is>
       </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>岛间岬</t>
-        </is>
-      </c>
-      <c r="D277" s="4" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>岛间崎</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E277" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F277" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr"/>
+      <c r="E277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -9438,36 +9438,36 @@
       <c r="H279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="n">
+      <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="B280" s="4" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>旧種子島空港跡</t>
         </is>
       </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>旧种子岛机场遗址</t>
-        </is>
-      </c>
-      <c r="D280" s="4" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>旧种子岛机场旧址</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>地名</t>
         </is>
       </c>
-      <c r="E280" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F280" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H280" s="5" t="inlineStr"/>
+      <c r="E280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -11838,36 +11838,36 @@
       <c r="H354" s="5" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="4" t="n">
+      <c r="A355" s="2" t="n">
         <v>354</v>
       </c>
-      <c r="B355" s="4" t="inlineStr">
+      <c r="B355" s="2" t="inlineStr">
         <is>
           <t>しほり</t>
         </is>
       </c>
-      <c r="C355" s="4" t="inlineStr">
-        <is>
-          <t>志穂里</t>
-        </is>
-      </c>
-      <c r="D355" s="4" t="inlineStr">
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>志穗里</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
         <is>
           <t>女性人名</t>
         </is>
       </c>
-      <c r="E355" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F355" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G355" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H355" s="5" t="inlineStr"/>
+      <c r="E355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -12030,36 +12030,36 @@
       <c r="H360" s="3" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="4" t="n">
+      <c r="A361" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="B361" s="4" t="inlineStr">
+      <c r="B361" s="2" t="inlineStr">
         <is>
           <t>フェイリス・ニャンニャン</t>
         </is>
       </c>
-      <c r="C361" s="4" t="inlineStr">
-        <is>
-          <t>菲莉丝·喵喵</t>
-        </is>
-      </c>
-      <c r="D361" s="4" t="inlineStr">
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>菲莉丝・喵喵</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
         <is>
           <t>女性人名</t>
         </is>
       </c>
-      <c r="E361" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F361" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G361" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H361" s="5" t="inlineStr"/>
+      <c r="E361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H361" s="3" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -12670,36 +12670,36 @@
       <c r="H380" s="3" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="4" t="n">
+      <c r="A381" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="B381" s="4" t="inlineStr">
+      <c r="B381" s="2" t="inlineStr">
         <is>
           <t>ジャネ</t>
         </is>
       </c>
-      <c r="C381" s="4" t="inlineStr">
-        <is>
-          <t>珍妮</t>
-        </is>
-      </c>
-      <c r="D381" s="4" t="inlineStr">
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>詹内</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
         <is>
           <t>未知性别人名</t>
         </is>
       </c>
-      <c r="E381" s="4" t="n">
+      <c r="E381" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F381" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G381" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H381" s="5" t="inlineStr"/>
+      <c r="F381" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H381" s="3" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="4" t="n">
@@ -13150,36 +13150,36 @@
       <c r="H395" s="3" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="4" t="n">
+      <c r="A396" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="B396" s="4" t="inlineStr">
+      <c r="B396" s="2" t="inlineStr">
         <is>
           <t>コスモ</t>
         </is>
       </c>
-      <c r="C396" s="4" t="inlineStr">
-        <is>
-          <t>Cosmo</t>
-        </is>
-      </c>
-      <c r="D396" s="4" t="inlineStr">
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>小宇宙</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E396" s="4" t="n">
+      <c r="E396" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F396" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G396" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H396" s="5" t="inlineStr"/>
+      <c r="F396" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="H396" s="3" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -13246,36 +13246,36 @@
       <c r="H398" s="3" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="n">
+      <c r="A399" s="2" t="n">
         <v>398</v>
       </c>
-      <c r="B399" s="4" t="inlineStr">
+      <c r="B399" s="2" t="inlineStr">
         <is>
           <t>アッチャメ・キック</t>
         </is>
       </c>
-      <c r="C399" s="4" t="inlineStr">
-        <is>
-          <t>阿恰美·飞踢</t>
-        </is>
-      </c>
-      <c r="D399" s="4" t="inlineStr">
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>阿恰美・飞踢</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E399" s="4" t="n">
+      <c r="E399" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F399" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G399" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H399" s="5" t="inlineStr"/>
+      <c r="F399" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H399" s="3" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -13406,36 +13406,36 @@
       <c r="H403" s="3" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="4" t="n">
+      <c r="A404" s="2" t="n">
         <v>403</v>
       </c>
-      <c r="B404" s="4" t="inlineStr">
+      <c r="B404" s="2" t="inlineStr">
         <is>
           <t>あっちゃめ・ぱーんち</t>
         </is>
       </c>
-      <c r="C404" s="4" t="inlineStr">
-        <is>
-          <t>阿恰美·重拳</t>
-        </is>
-      </c>
-      <c r="D404" s="4" t="inlineStr">
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>阿恰美・重拳</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E404" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F404" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G404" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H404" s="5" t="inlineStr"/>
+      <c r="E404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H404" s="3" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -13470,68 +13470,68 @@
       <c r="H405" s="3" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="4" t="n">
+      <c r="A406" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="B406" s="4" t="inlineStr">
+      <c r="B406" s="2" t="inlineStr">
         <is>
           <t>アッチャメ・パンチ</t>
         </is>
       </c>
-      <c r="C406" s="4" t="inlineStr">
-        <is>
-          <t>阿恰美·重拳</t>
-        </is>
-      </c>
-      <c r="D406" s="4" t="inlineStr">
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>阿恰美・重拳</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E406" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F406" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G406" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H406" s="5" t="inlineStr"/>
+      <c r="E406" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H406" s="3" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="4" t="n">
+      <c r="A407" s="2" t="n">
         <v>406</v>
       </c>
-      <c r="B407" s="4" t="inlineStr">
+      <c r="B407" s="2" t="inlineStr">
         <is>
           <t>アトラス・パーンチ</t>
         </is>
       </c>
-      <c r="C407" s="4" t="inlineStr">
-        <is>
-          <t>阿特拉斯·重拳</t>
-        </is>
-      </c>
-      <c r="D407" s="4" t="inlineStr">
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>阿特拉斯・重拳</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E407" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F407" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G407" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H407" s="5" t="inlineStr"/>
+      <c r="E407" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H407" s="3" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -13566,36 +13566,36 @@
       <c r="H408" s="3" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="n">
+      <c r="A409" s="2" t="n">
         <v>408</v>
       </c>
-      <c r="B409" s="4" t="inlineStr">
+      <c r="B409" s="2" t="inlineStr">
         <is>
           <t>タネガシマン・フラッシュ</t>
         </is>
       </c>
-      <c r="C409" s="4" t="inlineStr">
-        <is>
-          <t>种子岛侠·闪光</t>
-        </is>
-      </c>
-      <c r="D409" s="4" t="inlineStr">
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>种子岛侠・闪光</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
         <is>
           <t>特殊技能</t>
         </is>
       </c>
-      <c r="E409" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F409" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G409" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H409" s="5" t="inlineStr"/>
+      <c r="E409" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H409" s="3" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -15582,36 +15582,36 @@
       <c r="H471" s="3" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="4" t="n">
+      <c r="A472" s="2" t="n">
         <v>471</v>
       </c>
-      <c r="B472" s="4" t="inlineStr">
+      <c r="B472" s="2" t="inlineStr">
         <is>
           <t>たけこぷかめらー</t>
         </is>
       </c>
-      <c r="C472" s="4" t="inlineStr">
-        <is>
-          <t>竹蜻蜓摄像机</t>
-        </is>
-      </c>
-      <c r="D472" s="4" t="inlineStr">
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>竹蜻蜓照相机</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
         <is>
           <t>特殊物品</t>
         </is>
       </c>
-      <c r="E472" s="4" t="n">
+      <c r="E472" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F472" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G472" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H472" s="5" t="inlineStr"/>
+      <c r="F472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H472" s="3" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -15678,36 +15678,36 @@
       <c r="H474" s="3" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="4" t="n">
+      <c r="A475" s="2" t="n">
         <v>474</v>
       </c>
-      <c r="B475" s="4" t="inlineStr">
+      <c r="B475" s="2" t="inlineStr">
         <is>
           <t>スーパー・スバルロボ</t>
         </is>
       </c>
-      <c r="C475" s="4" t="inlineStr">
-        <is>
-          <t>超级昴天神</t>
-        </is>
-      </c>
-      <c r="D475" s="4" t="inlineStr">
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>超级昴星神</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
         <is>
           <t>特殊物品</t>
         </is>
       </c>
-      <c r="E475" s="4" t="n">
+      <c r="E475" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F475" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G475" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H475" s="5" t="inlineStr"/>
+      <c r="F475" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -15806,36 +15806,36 @@
       <c r="H478" s="3" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="4" t="n">
+      <c r="A479" s="2" t="n">
         <v>478</v>
       </c>
-      <c r="B479" s="4" t="inlineStr">
+      <c r="B479" s="2" t="inlineStr">
         <is>
           <t>ペドグリーチャム</t>
         </is>
       </c>
-      <c r="C479" s="4" t="inlineStr">
-        <is>
-          <t>宝璐狗粮</t>
-        </is>
-      </c>
-      <c r="D479" s="4" t="inlineStr">
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>宝璐</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
         <is>
           <t>特殊物品</t>
         </is>
       </c>
-      <c r="E479" s="4" t="n">
+      <c r="E479" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F479" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G479" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H479" s="5" t="inlineStr"/>
+      <c r="F479" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H479" s="3" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>索普拉诺</t>
+          <t>Soprano（车型名）</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Homeros</t>
+          <t>Homer（车型名）</t>
         </is>
       </c>
       <c r="D498" s="4" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>拉拉面包</t>
+          <t>Lapin（车型名）</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -16638,36 +16638,36 @@
       <c r="H504" s="3" t="inlineStr"/>
     </row>
     <row r="505">
-      <c r="A505" s="4" t="n">
+      <c r="A505" s="2" t="n">
         <v>504</v>
       </c>
-      <c r="B505" s="4" t="inlineStr">
+      <c r="B505" s="2" t="inlineStr">
         <is>
           <t>次世代型エンジン</t>
         </is>
       </c>
-      <c r="C505" s="4" t="inlineStr">
-        <is>
-          <t>次世代型引擎</t>
-        </is>
-      </c>
-      <c r="D505" s="4" t="inlineStr">
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>次世代引擎</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
         <is>
           <t>特殊物品</t>
         </is>
       </c>
-      <c r="E505" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F505" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G505" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H505" s="5" t="inlineStr"/>
+      <c r="E505" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H505" s="3" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -17346,36 +17346,36 @@
       <c r="H526" s="3" t="inlineStr"/>
     </row>
     <row r="527">
-      <c r="A527" s="4" t="n">
+      <c r="A527" s="2" t="n">
         <v>526</v>
       </c>
-      <c r="B527" s="4" t="inlineStr">
+      <c r="B527" s="2" t="inlineStr">
         <is>
           <t>ホトクリン</t>
         </is>
       </c>
-      <c r="C527" s="4" t="inlineStr">
-        <is>
-          <t>霍托克林</t>
-        </is>
-      </c>
-      <c r="D527" s="4" t="inlineStr">
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>Hotokurin</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
         <is>
           <t>特殊生物</t>
         </is>
       </c>
-      <c r="E527" s="4" t="n">
+      <c r="E527" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F527" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G527" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H527" s="5" t="inlineStr"/>
+      <c r="F527" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H527" s="3" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -19644,7 +19644,7 @@
         <v>7</v>
       </c>
       <c r="F598" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>5</v>
       </c>
       <c r="F600" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G600" s="2" t="inlineStr">
         <is>
@@ -20102,36 +20102,36 @@
       <c r="H612" s="3" t="inlineStr"/>
     </row>
     <row r="613">
-      <c r="A613" s="4" t="n">
+      <c r="A613" s="2" t="n">
         <v>612</v>
       </c>
-      <c r="B613" s="4" t="inlineStr">
+      <c r="B613" s="2" t="inlineStr">
         <is>
           <t>メイド喫茶客</t>
         </is>
       </c>
-      <c r="C613" s="4" t="inlineStr">
+      <c r="C613" s="2" t="inlineStr">
         <is>
           <t>女仆咖啡厅顾客</t>
         </is>
       </c>
-      <c r="D613" s="4" t="inlineStr">
+      <c r="D613" s="2" t="inlineStr">
         <is>
           <t>男性人名</t>
         </is>
       </c>
-      <c r="E613" s="4" t="n">
+      <c r="E613" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F613" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G613" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H613" s="5" t="inlineStr"/>
+      <c r="F613" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H613" s="3" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -20390,68 +20390,68 @@
       <c r="H621" s="3" t="inlineStr"/>
     </row>
     <row r="622">
-      <c r="A622" s="4" t="n">
+      <c r="A622" s="2" t="n">
         <v>621</v>
       </c>
-      <c r="B622" s="4" t="inlineStr">
+      <c r="B622" s="2" t="inlineStr">
         <is>
           <t>タネガイエロー・チュウタ</t>
         </is>
       </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>种子岛・Yellow・中太</t>
-        </is>
-      </c>
-      <c r="D622" s="4" t="inlineStr">
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>种子岛・黄・中太</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
         <is>
           <t>男性人名</t>
         </is>
       </c>
-      <c r="E622" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F622" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G622" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H622" s="5" t="inlineStr"/>
+      <c r="E622" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F622" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H622" s="3" t="inlineStr"/>
     </row>
     <row r="623">
-      <c r="A623" s="4" t="n">
+      <c r="A623" s="2" t="n">
         <v>622</v>
       </c>
-      <c r="B623" s="4" t="inlineStr">
+      <c r="B623" s="2" t="inlineStr">
         <is>
           <t>タネガ・イエロウ・チュウタ</t>
         </is>
       </c>
-      <c r="C623" s="4" t="inlineStr">
-        <is>
-          <t>种子岛・Yellow・中太</t>
-        </is>
-      </c>
-      <c r="D623" s="4" t="inlineStr">
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>种子岛・黄・中太</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
         <is>
           <t>男性人名</t>
         </is>
       </c>
-      <c r="E623" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F623" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G623" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H623" s="5" t="inlineStr"/>
+      <c r="E623" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F623" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H623" s="3" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
@@ -22086,36 +22086,36 @@
       <c r="H674" s="3" t="inlineStr"/>
     </row>
     <row r="675">
-      <c r="A675" s="4" t="n">
+      <c r="A675" s="2" t="n">
         <v>674</v>
       </c>
-      <c r="B675" s="4" t="inlineStr">
+      <c r="B675" s="2" t="inlineStr">
         <is>
           <t>西之表市経済観光課</t>
         </is>
       </c>
-      <c r="C675" s="4" t="inlineStr">
-        <is>
-          <t>西之表市经济观光科</t>
-        </is>
-      </c>
-      <c r="D675" s="4" t="inlineStr">
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>西之表市经济观光课</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E675" s="4" t="n">
+      <c r="E675" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F675" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G675" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H675" s="5" t="inlineStr"/>
+      <c r="F675" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H675" s="3" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
@@ -22374,36 +22374,36 @@
       <c r="H683" s="3" t="inlineStr"/>
     </row>
     <row r="684">
-      <c r="A684" s="4" t="n">
+      <c r="A684" s="2" t="n">
         <v>683</v>
       </c>
-      <c r="B684" s="4" t="inlineStr">
+      <c r="B684" s="2" t="inlineStr">
         <is>
           <t>南日本酪農協同</t>
         </is>
       </c>
-      <c r="C684" s="4" t="inlineStr">
-        <is>
-          <t>南日本酪农乳业</t>
-        </is>
-      </c>
-      <c r="D684" s="4" t="inlineStr">
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>南日本酪农协同</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E684" s="4" t="n">
+      <c r="E684" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F684" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G684" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H684" s="5" t="inlineStr"/>
+      <c r="F684" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H684" s="3" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
@@ -22662,36 +22662,36 @@
       <c r="H692" s="3" t="inlineStr"/>
     </row>
     <row r="693">
-      <c r="A693" s="4" t="n">
+      <c r="A693" s="2" t="n">
         <v>692</v>
       </c>
-      <c r="B693" s="4" t="inlineStr">
+      <c r="B693" s="2" t="inlineStr">
         <is>
           <t>エグスケ</t>
         </is>
       </c>
-      <c r="C693" s="4" t="inlineStr">
-        <is>
-          <t>Exkee</t>
-        </is>
-      </c>
-      <c r="D693" s="4" t="inlineStr">
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>Exoskeleton公司</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E693" s="4" t="n">
+      <c r="E693" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F693" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G693" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H693" s="5" t="inlineStr"/>
+      <c r="F693" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H693" s="3" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
@@ -23206,36 +23206,36 @@
       <c r="H709" s="3" t="inlineStr"/>
     </row>
     <row r="710">
-      <c r="A710" s="4" t="n">
+      <c r="A710" s="2" t="n">
         <v>709</v>
       </c>
-      <c r="B710" s="4" t="inlineStr">
+      <c r="B710" s="2" t="inlineStr">
         <is>
           <t>USロボコム社</t>
         </is>
       </c>
-      <c r="C710" s="4" t="inlineStr">
-        <is>
-          <t>US罗伯康公司</t>
-        </is>
-      </c>
-      <c r="D710" s="4" t="inlineStr">
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>US机器人公司</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E710" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F710" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G710" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H710" s="5" t="inlineStr"/>
+      <c r="E710" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F710" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H710" s="3" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
@@ -23782,36 +23782,36 @@
       <c r="H727" s="3" t="inlineStr"/>
     </row>
     <row r="728">
-      <c r="A728" s="4" t="n">
+      <c r="A728" s="2" t="n">
         <v>727</v>
       </c>
-      <c r="B728" s="4" t="inlineStr">
+      <c r="B728" s="2" t="inlineStr">
         <is>
           <t>南九州SX予備校</t>
         </is>
       </c>
-      <c r="C728" s="4" t="inlineStr">
-        <is>
-          <t>南九州SX补习班</t>
-        </is>
-      </c>
-      <c r="D728" s="4" t="inlineStr">
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>南九州SX预备校</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E728" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F728" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G728" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H728" s="5" t="inlineStr"/>
+      <c r="E728" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F728" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H728" s="3" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
@@ -23974,36 +23974,36 @@
       <c r="H733" s="3" t="inlineStr"/>
     </row>
     <row r="734">
-      <c r="A734" s="4" t="n">
+      <c r="A734" s="2" t="n">
         <v>733</v>
       </c>
-      <c r="B734" s="4" t="inlineStr">
+      <c r="B734" s="2" t="inlineStr">
         <is>
           <t>株式会社シアワセ4U</t>
         </is>
       </c>
-      <c r="C734" s="4" t="inlineStr">
-        <is>
-          <t>幸福4U股份有限公司</t>
-        </is>
-      </c>
-      <c r="D734" s="4" t="inlineStr">
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>幸福4U有限公司</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="E734" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F734" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G734" s="4" t="inlineStr">
-        <is>
-          <t>★未落实</t>
-        </is>
-      </c>
-      <c r="H734" s="5" t="inlineStr"/>
+      <c r="E734" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F734" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H734" s="3" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="4" t="n">
@@ -25405,7 +25405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25444,7 +25444,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26 00:13</t>
+          <t>2026-09-26 02:06</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25586,67 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>★ 黄底「未落实」的 36 条经逐条核查，均属下列情形，不是缺陷：</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 有意保留日文：_system_00 的曲名/制作署名（志倉千代丸、南條愛乃、いとうかなこ 等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. 保留原厂拉丁名：geotag 车辆登记栏的车型（Suzuki・Soprano、CONDA・Homer、Suzuki・Lapin 等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. TIPS 槽位错位：原文在槽 N、译文落在槽 N+1（属已知上游问题，用户裁定暂缓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. 子串误命中：如 雌龍の岩 是 雄龍・雌龍の岩 的子串，表内另有精确条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. 体例差异：读音槽填罗马音（非中文），表条目在该位置不适用</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. 待用户裁定：ツマ崎/コンドリア大学/ボスケテ/あっぽ~らんど/コスモポート種子島 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>本表取代了仓库里旧的 glossary（旧）.xlsx（558 行，仅 557 条，且译名已过时）。</t>
         </is>
